--- a/data/b2_centro/B2 Centro 11-2025.xlsx
+++ b/data/b2_centro/B2 Centro 11-2025.xlsx
@@ -4779,79 +4779,79 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1628.26</v>
+        <v>1485.24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>45966</v>
+        <v>45964</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>78788.98</v>
+        <v>2366.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>45970</v>
+        <v>45965</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2027.74</v>
+        <v>3318.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>45970</v>
+        <v>45966</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>5980.23</v>
+        <v>78523.35000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>45971</v>
+        <v>45970</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>38000</v>
+        <v>5893.61</v>
       </c>
     </row>
     <row r="7">
@@ -4860,52 +4860,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4300</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>45973</v>
+        <v>45971</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2099.13</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>45974</v>
+        <v>45973</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1380.93</v>
+        <v>2053.34</v>
       </c>
     </row>
     <row r="10">
@@ -4923,7 +4923,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>13708.44</v>
+        <v>13198.43</v>
       </c>
     </row>
     <row r="11">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>4195.17</v>
+        <v>3829.75</v>
       </c>
     </row>
     <row r="12">
@@ -4959,43 +4959,43 @@
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>5335.28</v>
+        <v>5846.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>45981</v>
+        <v>45980</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>27742.88</v>
+        <v>2493.41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>45983</v>
+        <v>45981</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>4936.73</v>
+        <v>27671.3</v>
       </c>
     </row>
     <row r="15">
@@ -5004,39 +5004,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>5340.64</v>
+        <v>1813.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>45986</v>
+        <v>45984</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>3996.53</v>
+        <v>5405.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>45987</v>
+        <v>45986</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -5045,11 +5045,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>1320.28</v>
+        <v>2615.9</v>
       </c>
     </row>
     <row r="18">
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>5427.07</v>
+        <v>5350.34</v>
       </c>
     </row>
   </sheetData>
